--- a/excel/atuq-dex-s-a-c_ccc.xlsx
+++ b/excel/atuq-dex-s-a-c_ccc.xlsx
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13512</v>
+        <v>7193</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C001115436</t>
+          <t>C001022667</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C001115436 - PALACIOS LADINES CARMEN SARA</t>
+          <t>C001022667 - RIOFRIO CORREA ROSA ADELA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17850640</t>
+          <t>S17842579</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -713,19 +713,19 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7193</v>
+        <v>13512</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C001022667</t>
+          <t>C001115436</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C001022667 - RIOFRIO CORREA ROSA ADELA</t>
+          <t>C001115436 - PALACIOS LADINES CARMEN SARA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17842579</t>
+          <t>S17850640</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38866</v>
+        <v>41471</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C001578374</t>
+          <t>C001507871</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C001578374 - NOLE AGUIRRE MARLON HERLIN</t>
+          <t>C001507871 - ALAMA BARRETO CRISTHIAN ALEXIS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17849537</t>
+          <t>S17833860</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41471</v>
+        <v>38866</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C001507871</t>
+          <t>C001578374</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C001507871 - ALAMA BARRETO CRISTHIAN ALEXIS</t>
+          <t>C001578374 - NOLE AGUIRRE MARLON HERLIN</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17833860</t>
+          <t>S17849537</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2349,7 +2349,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>74259</v>
+        <v>77519</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C004208838</t>
+          <t>C004216207</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C004208838 - HIDALGO SUNCION ESDGAR MIGUEL</t>
+          <t>C004216207 - MADRID TORRES ZOILA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17812480</t>
+          <t>S17811623</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2448,24 +2448,24 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>77519</v>
+        <v>74259</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C004216207</t>
+          <t>C004208838</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C004216207 - MADRID TORRES ZOILA</t>
+          <t>C004208838 - HIDALGO SUNCION ESDGAR MIGUEL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17811623</t>
+          <t>S17812480</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,17 +2564,17 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60494</v>
+        <v>63822</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C001767333</t>
+          <t>C004100055</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C001767333 - AQUINO FARFAN MARIA AURISTELA</t>
+          <t>C004100055 - TINEO DE LA CRUZ FRANCISCA JANNET</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17773360</t>
+          <t>S17775328</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3509,7 +3509,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>63822</v>
+        <v>66162</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C004100055</t>
+          <t>C004217154</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C004100055 - TINEO DE LA CRUZ FRANCISCA JANNET</t>
+          <t>C004217154 - MARCHENA TACURE CRISTINO</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17775328</t>
+          <t>S17776062</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3625,7 +3625,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66162</v>
+        <v>65642</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C004217154</t>
+          <t>C001768340</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C004217154 - MARCHENA TACURE CRISTINO</t>
+          <t>C001768340 - TOLEDO DE SALDARRIAGA MARIA AURORA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17776062</t>
+          <t>S17786931</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3741,7 +3741,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>65642</v>
+        <v>60494</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001768340</t>
+          <t>C001767333</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001768340 - TOLEDO DE SALDARRIAGA MARIA AURORA</t>
+          <t>C001767333 - AQUINO FARFAN MARIA AURISTELA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17786931</t>
+          <t>S17773360</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3973,7 +3973,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56213</v>
+        <v>55704</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C001767070</t>
+          <t>C001767334</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C001767070 - HUAMAN AMANINGO TOBIAS</t>
+          <t>C001767334 - SANDOVAL URRUNAGA MARIBEL DEL CARMEN</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17770318</t>
+          <t>S17774276</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4089,7 +4089,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55704</v>
+        <v>56213</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4123,12 +4123,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C001767334</t>
+          <t>C001767070</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C001767334 - SANDOVAL URRUNAGA MARIBEL DEL CARMEN</t>
+          <t>C001767070 - HUAMAN AMANINGO TOBIAS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17774276</t>
+          <t>S17770318</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5481,7 +5481,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>89682</v>
+        <v>80138</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C001583752</t>
+          <t>C004248775</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C001583752 - CAMACHO CURAY ROCIO DEL PILAR</t>
+          <t>C004248775 - Juana Diaz Nunez</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17737317</t>
+          <t>S17736806</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5585,19 +5585,19 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>70647</v>
+        <v>89682</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C004062737</t>
+          <t>C001583752</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C004062737 - REYES AVALOS DORA ALICIA</t>
+          <t>C001583752 - CAMACHO CURAY ROCIO DEL PILAR</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>S17746066</t>
+          <t>S17737317</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>72930</v>
+        <v>70647</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C004100374</t>
+          <t>C004062737</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C004100374 - CARRENO SANCHEZ ANALI PAOLA</t>
+          <t>C004062737 - REYES AVALOS DORA ALICIA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S17740612</t>
+          <t>S17746066</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>80138</v>
+        <v>72930</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C004248775</t>
+          <t>C004100374</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C004248775 - Juana Diaz Nunez</t>
+          <t>C004100374 - CARRENO SANCHEZ ANALI PAOLA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S17736806</t>
+          <t>S17740612</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7221,7 +7221,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5401</v>
+        <v>5028</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7255,12 +7255,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C001019082</t>
+          <t>C001024784</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C001019082 - VILLEGAS CASTILLO HILDEBRANDO</t>
+          <t>C001024784 - PALACIOS CARCAMO ESTHER</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S17717830</t>
+          <t>S17710539</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7320,7 +7320,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -7330,14 +7330,14 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5028</v>
+        <v>5401</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C001024784</t>
+          <t>C001019082</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C001024784 - PALACIOS CARCAMO ESTHER</t>
+          <t>C001019082 - VILLEGAS CASTILLO HILDEBRANDO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>S17710539</t>
+          <t>S17717830</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7436,7 +7436,7 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>89092</v>
+        <v>92456</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8183,12 +8183,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C001705048</t>
+          <t>C004207450</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C001705048 - RIVERA ABAD CELIA</t>
+          <t>C004207450 - PAREDES SAAVEDRA JORGE DEMETRIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>S17712765</t>
+          <t>S17714352</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
@@ -8381,7 +8381,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>92456</v>
+        <v>91607</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>C004207450</t>
+          <t>C004098265</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C004207450 - PAREDES SAAVEDRA JORGE DEMETRIO</t>
+          <t>C004098265 - BECERRA MAYO DIANA CAROLINA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>S17714352</t>
+          <t>S17719250</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8490,14 +8490,14 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>91607</v>
+        <v>89092</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8531,12 +8531,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>C004098265</t>
+          <t>C001705048</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C004098265 - BECERRA MAYO DIANA CAROLINA</t>
+          <t>C001705048 - RIVERA ABAD CELIA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>S17719250</t>
+          <t>S17712765</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr"/>
@@ -9309,7 +9309,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>99995</v>
+        <v>107531</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -9343,12 +9343,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>C004187393</t>
+          <t>C001024806</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>C004187393 - RIVERA ZAPATA MARCELA MAGALLI</t>
+          <t>C001024806 - LUNA GONZALES BELINDA ROSMERY</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>S17686133</t>
+          <t>S17687337</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9425,7 +9425,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>102664</v>
+        <v>99995</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -9459,12 +9459,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>C001666015</t>
+          <t>C004187393</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C001666015 - SUSSONI CORREA MAGGALI FANNY</t>
+          <t>C004187393 - RIVERA ZAPATA MARCELA MAGALLI</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>S17695978</t>
+          <t>S17686133</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9541,7 +9541,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>107531</v>
+        <v>102664</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -9575,12 +9575,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>C001024806</t>
+          <t>C001666015</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>C001024806 - LUNA GONZALES BELINDA ROSMERY</t>
+          <t>C001666015 - SUSSONI CORREA MAGGALI FANNY</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>S17687337</t>
+          <t>S17695978</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10005,7 +10005,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>67220</v>
+        <v>66993</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>C004163714</t>
+          <t>C004174726</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>C004163714 - LLAGUENTA MONJE DINA LUZ</t>
+          <t>C004174726 - FARFAN MACALUPU ISRAEL CARLOS DAVID</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>S17683208</t>
+          <t>S17705433</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10104,12 +10104,12 @@
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10121,7 +10121,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>66993</v>
+        <v>67220</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -10155,12 +10155,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>C004174726</t>
+          <t>C004163714</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>C004174726 - FARFAN MACALUPU ISRAEL CARLOS DAVID</t>
+          <t>C004163714 - LLAGUENTA MONJE DINA LUZ</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>S17705433</t>
+          <t>S17683208</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10220,12 +10220,12 @@
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12429,16 +12429,16 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>52954</v>
+        <v>54136</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EDITH GRANADOS CHAPOÑAN</t>
+          <t>ANDERSON DENIS GARCIA PASACHE</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>47812071</t>
+          <t>47180093</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TUMBES</t>
+          <t>SULLANA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -12463,17 +12463,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>C001755662</t>
+          <t>C001765793</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>C001755662 - OCUPA ADRIANZEN OMAR ADAN</t>
+          <t>C001765793 - ESPINOZA PRIETO SERGIO JUNIOR</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1000036415</t>
+          <t>1000036414</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -12488,11 +12488,11 @@
         <v>46235</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>S17741726</t>
+          <t>S17787834</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12502,11 +12502,11 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>47812071TUMBESGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000036415</t>
+          <t>47180093SULLANAGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000036414</t>
         </is>
       </c>
       <c r="R104" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -12533,28 +12533,28 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>54136</v>
+        <v>52954</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ANDERSON DENIS GARCIA PASACHE</t>
+          <t>EDITH GRANADOS CHAPOÑAN</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>47180093</t>
+          <t>47812071</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SULLANA</t>
+          <t>TUMBES</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -12579,17 +12579,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>C001765793</t>
+          <t>C001755662</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>C001765793 - ESPINOZA PRIETO SERGIO JUNIOR</t>
+          <t>C001755662 - OCUPA ADRIANZEN OMAR ADAN</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1000036414</t>
+          <t>1000036415</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -12604,11 +12604,11 @@
         <v>46235</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>S17787834</t>
+          <t>S17741726</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12618,11 +12618,11 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>47180093SULLANAGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000036414</t>
+          <t>47812071TUMBESGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000036415</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -12649,12 +12649,12 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr"/>
@@ -13345,7 +13345,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>86004</v>
+        <v>92536</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>C004242092</t>
+          <t>C004244609</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>C004242092 - SEMINARIO ZEGARRA MARLON ALONSO</t>
+          <t>C004244609 - Maria Isabel Navarro More</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13404,11 +13404,11 @@
         <v>46235</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>S17624391</t>
+          <t>S17788901</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -13444,7 +13444,7 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -13454,14 +13454,14 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>92536</v>
+        <v>86004</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>C004244609</t>
+          <t>C004242092</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>C004244609 - Maria Isabel Navarro More</t>
+          <t>C004242092 - SEMINARIO ZEGARRA MARLON ALONSO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13520,11 +13520,11 @@
         <v>46235</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>S17788901</t>
+          <t>S17624391</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13560,7 +13560,7 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr"/>
@@ -13925,7 +13925,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>103440</v>
+        <v>106103</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -13959,12 +13959,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>C001663236</t>
+          <t>C001020352</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>C001663236 - ORDINOLA CARREÑO JESUS MARTIN</t>
+          <t>C001020352 - LUPU BARCO IRMA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13984,11 +13984,11 @@
         <v>46235</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>S17592032</t>
+          <t>S17654340</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Despacho solo permite pago en efectivo</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -14024,12 +14024,12 @@
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14041,7 +14041,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>106103</v>
+        <v>103440</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -14075,12 +14075,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>C001020352</t>
+          <t>C001663236</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>C001020352 - LUPU BARCO IRMA</t>
+          <t>C001663236 - ORDINOLA CARREÑO JESUS MARTIN</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14100,11 +14100,11 @@
         <v>46235</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>S17654340</t>
+          <t>S17592032</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Despacho solo permite pago en efectivo</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14140,12 +14140,12 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14273,7 +14273,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>90289</v>
+        <v>86526</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -14307,12 +14307,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>C001680295</t>
+          <t>C001508451</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>C001680295 - CORDOVA BECERRA IKE KEVIN</t>
+          <t>C001508451 - RODRIGUEZ VIERA FLOR MARIA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>S17610804</t>
+          <t>S17592577</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -14382,14 +14382,14 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>86526</v>
+        <v>90289</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -14423,12 +14423,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>C001508451</t>
+          <t>C001680295</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>C001508451 - RODRIGUEZ VIERA FLOR MARIA</t>
+          <t>C001680295 - CORDOVA BECERRA IKE KEVIN</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>S17592577</t>
+          <t>S17610804</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -14498,14 +14498,14 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>78232</v>
+        <v>78122</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -14539,12 +14539,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>C004174809</t>
+          <t>C004178803</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>C004174809 - MADRID OLAYA HEINER ANTONIO</t>
+          <t>C004178803 - MARCELO BECERRA BETTY RUTH</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>S17583761</t>
+          <t>S17584711</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14604,24 +14604,24 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>78122</v>
+        <v>78232</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -14655,12 +14655,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>C004178803</t>
+          <t>C004174809</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>C004178803 - MARCELO BECERRA BETTY RUTH</t>
+          <t>C004174809 - MADRID OLAYA HEINER ANTONIO</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>S17584711</t>
+          <t>S17583761</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14720,17 +14720,17 @@
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
@@ -16129,7 +16129,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6935</v>
+        <v>8896</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -16163,12 +16163,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>C001018496</t>
+          <t>C001019126</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>C001018496 - ZAPATA MORAN MARTHA JOAQUINA</t>
+          <t>C001019126 - JIMENEZ CAMPOS ANTONIO</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -16188,11 +16188,11 @@
         <v>46235</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>S17571501</t>
+          <t>S17589148</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16245,7 +16245,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>8896</v>
+        <v>6935</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -16279,12 +16279,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>C001019126</t>
+          <t>C001018496</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>C001019126 - JIMENEZ CAMPOS ANTONIO</t>
+          <t>C001018496 - ZAPATA MORAN MARTHA JOAQUINA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16304,11 +16304,11 @@
         <v>46235</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>S17589148</t>
+          <t>S17571501</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17869,7 +17869,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>87833</v>
+        <v>91112</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -17903,12 +17903,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>C004190489</t>
+          <t>C001766932</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>C004190489 - ORDINOLA ALVARADO NATIVIDAD</t>
+          <t>C001766932 - IMAN QUEVEDO MIRIAM LILIANA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17928,11 +17928,11 @@
         <v>46235</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>S17580963</t>
+          <t>S17557288</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -17985,7 +17985,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>91112</v>
+        <v>87833</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -18019,12 +18019,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>C001766932</t>
+          <t>C004190489</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>C001766932 - IMAN QUEVEDO MIRIAM LILIANA</t>
+          <t>C004190489 - ORDINOLA ALVARADO NATIVIDAD</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18044,11 +18044,11 @@
         <v>46235</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>S17557288</t>
+          <t>S17580963</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -18101,7 +18101,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>82395</v>
+        <v>85296</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -18135,12 +18135,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>C004183662</t>
+          <t>C001407954</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>C004183662 - ZAPATA JIMENEZ MONICA FABIOLA DEL CARMEN</t>
+          <t>C001407954 - MIRANDA ROMERO ROXANA CARMEN</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18160,11 +18160,11 @@
         <v>46235</v>
       </c>
       <c r="N153" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>S17571216</t>
+          <t>S17634278</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
@@ -18217,7 +18217,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>81063</v>
+        <v>81259</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -18251,12 +18251,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>C004187652</t>
+          <t>C004196610</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>C004187652 - Maribel Sullon  Mauricio</t>
+          <t>C004196610 - Andrea Chira  Navarro</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>S17558266</t>
+          <t>S17575865</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -18326,14 +18326,14 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>81259</v>
+        <v>81063</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>C004196610</t>
+          <t>C004187652</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>C004196610 - Andrea Chira  Navarro</t>
+          <t>C004187652 - Maribel Sullon  Mauricio</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>S17575865</t>
+          <t>S17558266</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -18442,14 +18442,14 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>85296</v>
+        <v>82395</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -18483,12 +18483,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>C001407954</t>
+          <t>C004183662</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>C001407954 - MIRANDA ROMERO ROXANA CARMEN</t>
+          <t>C004183662 - ZAPATA JIMENEZ MONICA FABIOLA DEL CARMEN</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -18508,11 +18508,11 @@
         <v>46235</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>S17634278</t>
+          <t>S17571216</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -19609,7 +19609,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>95936</v>
+        <v>93158</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -19643,12 +19643,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>C001766696</t>
+          <t>C004189585</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>C001766696 - CASTILLO JIMENEZ HAYDEE</t>
+          <t>C004189585 - Trinidad Cordova Castillo</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -19672,7 +19672,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>S17533061</t>
+          <t>S17529206</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -19695,7 +19695,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -19718,14 +19718,14 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>82331</v>
+        <v>95936</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -19759,12 +19759,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>C004179758</t>
+          <t>C001766696</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>C004179758 - CHINGUEL QUISPE YNES</t>
+          <t>C001766696 - CASTILLO JIMENEZ HAYDEE</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>S17528714</t>
+          <t>S17533061</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -19829,19 +19829,19 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>93158</v>
+        <v>82331</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -19875,12 +19875,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>C004189585</t>
+          <t>C004179758</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>C004189585 - Trinidad Cordova Castillo</t>
+          <t>C004179758 - CHINGUEL QUISPE YNES</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>S17529206</t>
+          <t>S17528714</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
